--- a/INVENTARIOS SIN PROYECTO.xlsx
+++ b/INVENTARIOS SIN PROYECTO.xlsx
@@ -9,8 +9,7 @@
     <sheet name="ARMAS" sheetId="1" state="hidden" r:id="rId1"/>
     <sheet name="ACCESORIOS" sheetId="2" state="hidden" r:id="rId2"/>
     <sheet name="COMUNICACIONES" sheetId="3" state="hidden" r:id="rId3"/>
-    <sheet name="1_COBRE_6" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="2_ORO_562" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="1_ORO_562" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -2455,7 +2454,7 @@
       </c>
       <c r="F3" s="143" t="inlineStr">
         <is>
-          <t>COBRE 6</t>
+          <t>ORO 562</t>
         </is>
       </c>
       <c r="G3" s="133" t="n"/>
@@ -2510,11 +2509,7 @@
       <c r="B5" s="33" t="n"/>
       <c r="C5" s="33" t="n"/>
       <c r="D5" s="33" t="n"/>
-      <c r="E5" s="33" t="inlineStr">
-        <is>
-          <t>MV92164G</t>
-        </is>
-      </c>
+      <c r="E5" s="33" t="inlineStr"/>
       <c r="F5" s="33" t="n"/>
       <c r="G5" s="133" t="n"/>
       <c r="H5" s="133" t="n"/>
@@ -2534,7 +2529,7 @@
         </is>
       </c>
       <c r="C6" s="33" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D6" s="39" t="inlineStr">
         <is>
@@ -2625,7 +2620,7 @@
       </c>
       <c r="E8" s="45" t="inlineStr">
         <is>
-          <t>752TUH4776</t>
+          <t>752EYQA172</t>
         </is>
       </c>
       <c r="F8" s="45" t="n"/>
@@ -2704,1171 +2699,8 @@
         </is>
       </c>
       <c r="B12" s="43" t="n"/>
-      <c r="C12" s="43" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D12" s="146" t="n"/>
-      <c r="E12" s="133" t="n"/>
-      <c r="F12" s="133" t="n"/>
-      <c r="G12" s="133" t="n"/>
-      <c r="H12" s="133" t="n"/>
-      <c r="I12" s="133" t="n"/>
-      <c r="J12" s="133" t="n"/>
-      <c r="K12" s="134" t="n"/>
-    </row>
-    <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="40" t="inlineStr">
-        <is>
-          <t>PLACA KEVLAR</t>
-        </is>
-      </c>
-      <c r="B13" s="43" t="n"/>
-      <c r="C13" s="43" t="n">
-        <v>1</v>
-      </c>
-      <c r="D13" s="146" t="inlineStr">
-        <is>
-          <t>ECU55275 Y ECU55276</t>
-        </is>
-      </c>
-      <c r="E13" s="133" t="n"/>
-      <c r="F13" s="133" t="n"/>
-      <c r="G13" s="133" t="n"/>
-      <c r="H13" s="133" t="n"/>
-      <c r="I13" s="133" t="n"/>
-      <c r="J13" s="133" t="n"/>
-      <c r="K13" s="134" t="n"/>
-    </row>
-    <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="40" t="inlineStr">
-        <is>
-          <t>CINTO</t>
-        </is>
-      </c>
-      <c r="B14" s="43" t="n"/>
-      <c r="C14" s="43" t="n">
-        <v>1</v>
-      </c>
-      <c r="D14" s="146" t="n"/>
-      <c r="E14" s="133" t="n"/>
-      <c r="F14" s="133" t="n"/>
-      <c r="G14" s="133" t="n"/>
-      <c r="H14" s="133" t="n"/>
-      <c r="I14" s="133" t="n"/>
-      <c r="J14" s="133" t="n"/>
-      <c r="K14" s="134" t="n"/>
-    </row>
-    <row r="15" ht="18" customHeight="1">
-      <c r="A15" s="40" t="inlineStr">
-        <is>
-          <t>PORTA ARMA</t>
-        </is>
-      </c>
-      <c r="B15" s="43" t="n"/>
-      <c r="C15" s="43" t="n">
-        <v>1</v>
-      </c>
-      <c r="D15" s="146" t="n"/>
-      <c r="E15" s="133" t="n"/>
-      <c r="F15" s="133" t="n"/>
-      <c r="G15" s="133" t="n"/>
-      <c r="H15" s="133" t="n"/>
-      <c r="I15" s="133" t="n"/>
-      <c r="J15" s="133" t="n"/>
-      <c r="K15" s="134" t="n"/>
-    </row>
-    <row r="16" ht="18" customHeight="1">
-      <c r="A16" s="40" t="inlineStr">
-        <is>
-          <t>PORTA RADIO</t>
-        </is>
-      </c>
-      <c r="B16" s="43" t="n"/>
-      <c r="C16" s="43" t="n">
-        <v>1</v>
-      </c>
-      <c r="D16" s="146" t="n"/>
-      <c r="E16" s="133" t="n"/>
-      <c r="F16" s="133" t="n"/>
-      <c r="G16" s="133" t="n"/>
-      <c r="H16" s="133" t="n"/>
-      <c r="I16" s="133" t="n"/>
-      <c r="J16" s="133" t="n"/>
-      <c r="K16" s="134" t="n"/>
-    </row>
-    <row r="17" ht="18" customHeight="1">
-      <c r="A17" s="40" t="inlineStr">
-        <is>
-          <t>PORTA TOLETE</t>
-        </is>
-      </c>
-      <c r="B17" s="43" t="n"/>
-      <c r="C17" s="43" t="n">
-        <v>1</v>
-      </c>
-      <c r="D17" s="146" t="n"/>
-      <c r="E17" s="133" t="n"/>
-      <c r="F17" s="133" t="n"/>
-      <c r="G17" s="133" t="n"/>
-      <c r="H17" s="133" t="n"/>
-      <c r="I17" s="133" t="n"/>
-      <c r="J17" s="133" t="n"/>
-      <c r="K17" s="134" t="n"/>
-    </row>
-    <row r="18" ht="18" customHeight="1">
-      <c r="A18" s="40" t="inlineStr">
-        <is>
-          <t>TOLETE</t>
-        </is>
-      </c>
-      <c r="B18" s="43" t="n"/>
-      <c r="C18" s="43" t="n">
-        <v>1</v>
-      </c>
-      <c r="D18" s="146" t="n"/>
-      <c r="E18" s="133" t="n"/>
-      <c r="F18" s="133" t="n"/>
-      <c r="G18" s="133" t="n"/>
-      <c r="H18" s="133" t="n"/>
-      <c r="I18" s="133" t="n"/>
-      <c r="J18" s="133" t="n"/>
-      <c r="K18" s="134" t="n"/>
-    </row>
-    <row r="19" ht="18" customHeight="1">
-      <c r="A19" s="40" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PIERNERA </t>
-        </is>
-      </c>
-      <c r="B19" s="43" t="n"/>
-      <c r="C19" s="43" t="n"/>
-      <c r="D19" s="146" t="n"/>
-      <c r="E19" s="133" t="n"/>
-      <c r="F19" s="133" t="n"/>
-      <c r="G19" s="133" t="n"/>
-      <c r="H19" s="133" t="n"/>
-      <c r="I19" s="133" t="n"/>
-      <c r="J19" s="133" t="n"/>
-      <c r="K19" s="134" t="n"/>
-    </row>
-    <row r="20" ht="18" customHeight="1">
-      <c r="A20" s="40" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ESPOSAS </t>
-        </is>
-      </c>
-      <c r="B20" s="43" t="n"/>
-      <c r="C20" s="43" t="n"/>
-      <c r="D20" s="146" t="n"/>
-      <c r="E20" s="133" t="n"/>
-      <c r="F20" s="133" t="n"/>
-      <c r="G20" s="133" t="n"/>
-      <c r="H20" s="133" t="n"/>
-      <c r="I20" s="133" t="n"/>
-      <c r="J20" s="133" t="n"/>
-      <c r="K20" s="134" t="n"/>
-    </row>
-    <row r="21" ht="18" customHeight="1">
-      <c r="A21" s="40" t="inlineStr">
-        <is>
-          <t>CELULAR CORPORATIVO</t>
-        </is>
-      </c>
-      <c r="B21" s="43" t="n"/>
-      <c r="C21" s="43" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D21" s="146" t="n"/>
-      <c r="E21" s="133" t="n"/>
-      <c r="F21" s="133" t="n"/>
-      <c r="G21" s="133" t="n"/>
-      <c r="H21" s="133" t="n"/>
-      <c r="I21" s="133" t="n"/>
-      <c r="J21" s="133" t="n"/>
-      <c r="K21" s="134" t="n"/>
-    </row>
-    <row r="22" ht="18" customHeight="1">
-      <c r="A22" s="40" t="inlineStr">
-        <is>
-          <t xml:space="preserve">LINTERNA </t>
-        </is>
-      </c>
-      <c r="B22" s="43" t="n"/>
-      <c r="C22" s="43" t="n">
-        <v>1</v>
-      </c>
-      <c r="D22" s="146" t="n"/>
-      <c r="E22" s="133" t="n"/>
-      <c r="F22" s="133" t="n"/>
-      <c r="G22" s="133" t="n"/>
-      <c r="H22" s="133" t="n"/>
-      <c r="I22" s="133" t="n"/>
-      <c r="J22" s="133" t="n"/>
-      <c r="K22" s="134" t="n"/>
-    </row>
-    <row r="23" ht="18" customHeight="1">
-      <c r="A23" s="40" t="inlineStr">
-        <is>
-          <t>PONCHO IMPERMEABLE</t>
-        </is>
-      </c>
-      <c r="B23" s="43" t="n"/>
-      <c r="C23" s="43" t="n">
-        <v>1</v>
-      </c>
-      <c r="D23" s="146" t="n"/>
-      <c r="E23" s="133" t="n"/>
-      <c r="F23" s="133" t="n"/>
-      <c r="G23" s="133" t="n"/>
-      <c r="H23" s="133" t="n"/>
-      <c r="I23" s="133" t="n"/>
-      <c r="J23" s="133" t="n"/>
-      <c r="K23" s="134" t="n"/>
-    </row>
-    <row r="24" ht="18" customHeight="1">
-      <c r="A24" s="41" t="inlineStr">
-        <is>
-          <t>BOTAS DE IMPERMEABLES</t>
-        </is>
-      </c>
-      <c r="B24" s="43" t="n"/>
-      <c r="C24" s="43" t="n">
-        <v>1</v>
-      </c>
-      <c r="D24" s="146" t="n"/>
-      <c r="E24" s="133" t="n"/>
-      <c r="F24" s="133" t="n"/>
-      <c r="G24" s="133" t="n"/>
-      <c r="H24" s="133" t="n"/>
-      <c r="I24" s="133" t="n"/>
-      <c r="J24" s="133" t="n"/>
-      <c r="K24" s="134" t="n"/>
-    </row>
-    <row r="25" ht="18" customHeight="1">
-      <c r="A25" s="40" t="inlineStr">
-        <is>
-          <t>CHALECO LUMINOSO</t>
-        </is>
-      </c>
-      <c r="B25" s="43" t="n"/>
-      <c r="C25" s="43" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D25" s="146" t="n"/>
-      <c r="E25" s="133" t="n"/>
-      <c r="F25" s="133" t="n"/>
-      <c r="G25" s="133" t="n"/>
-      <c r="H25" s="133" t="n"/>
-      <c r="I25" s="133" t="n"/>
-      <c r="J25" s="133" t="n"/>
-      <c r="K25" s="134" t="n"/>
-    </row>
-    <row r="26" ht="18" customHeight="1">
-      <c r="A26" s="40" t="inlineStr">
-        <is>
-          <t>CASCO</t>
-        </is>
-      </c>
-      <c r="B26" s="43" t="n"/>
-      <c r="C26" s="43" t="n">
-        <v>1</v>
-      </c>
-      <c r="D26" s="146" t="n"/>
-      <c r="E26" s="133" t="n"/>
-      <c r="F26" s="133" t="n"/>
-      <c r="G26" s="133" t="n"/>
-      <c r="H26" s="133" t="n"/>
-      <c r="I26" s="133" t="n"/>
-      <c r="J26" s="133" t="n"/>
-      <c r="K26" s="134" t="n"/>
-    </row>
-    <row r="27" ht="18" customHeight="1">
-      <c r="A27" s="40" t="inlineStr">
-        <is>
-          <t>DETECTOR DE METALES</t>
-        </is>
-      </c>
-      <c r="B27" s="43" t="n"/>
-      <c r="C27" s="43" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D27" s="146" t="n"/>
-      <c r="E27" s="133" t="n"/>
-      <c r="F27" s="133" t="n"/>
-      <c r="G27" s="133" t="n"/>
-      <c r="H27" s="133" t="n"/>
-      <c r="I27" s="133" t="n"/>
-      <c r="J27" s="133" t="n"/>
-      <c r="K27" s="134" t="n"/>
-    </row>
-    <row r="28" ht="18" customHeight="1">
-      <c r="A28" s="40" t="inlineStr">
-        <is>
-          <t>SILBATO</t>
-        </is>
-      </c>
-      <c r="B28" s="43" t="n"/>
-      <c r="C28" s="43" t="n"/>
-      <c r="D28" s="146" t="n"/>
-      <c r="E28" s="133" t="n"/>
-      <c r="F28" s="133" t="n"/>
-      <c r="G28" s="133" t="n"/>
-      <c r="H28" s="133" t="n"/>
-      <c r="I28" s="133" t="n"/>
-      <c r="J28" s="133" t="n"/>
-      <c r="K28" s="134" t="n"/>
-    </row>
-    <row r="29" ht="18" customHeight="1">
-      <c r="A29" s="40" t="inlineStr">
-        <is>
-          <t>MESA</t>
-        </is>
-      </c>
-      <c r="B29" s="43" t="n"/>
-      <c r="C29" s="43" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D29" s="146" t="n"/>
-      <c r="E29" s="133" t="n"/>
-      <c r="F29" s="133" t="n"/>
-      <c r="G29" s="133" t="n"/>
-      <c r="H29" s="133" t="n"/>
-      <c r="I29" s="133" t="n"/>
-      <c r="J29" s="133" t="n"/>
-      <c r="K29" s="134" t="n"/>
-    </row>
-    <row r="30" ht="18" customHeight="1">
-      <c r="A30" s="40" t="inlineStr">
-        <is>
-          <t>SILLA</t>
-        </is>
-      </c>
-      <c r="B30" s="43" t="n"/>
-      <c r="C30" s="43" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D30" s="146" t="n"/>
-      <c r="E30" s="133" t="n"/>
-      <c r="F30" s="133" t="n"/>
-      <c r="G30" s="133" t="n"/>
-      <c r="H30" s="133" t="n"/>
-      <c r="I30" s="133" t="n"/>
-      <c r="J30" s="133" t="n"/>
-      <c r="K30" s="134" t="n"/>
-    </row>
-    <row r="31" ht="18" customHeight="1">
-      <c r="A31" s="40" t="inlineStr">
-        <is>
-          <t>CARPA</t>
-        </is>
-      </c>
-      <c r="B31" s="43" t="n"/>
-      <c r="C31" s="43" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D31" s="146" t="n"/>
-      <c r="E31" s="133" t="n"/>
-      <c r="F31" s="133" t="n"/>
-      <c r="G31" s="133" t="n"/>
-      <c r="H31" s="133" t="n"/>
-      <c r="I31" s="133" t="n"/>
-      <c r="J31" s="133" t="n"/>
-      <c r="K31" s="134" t="n"/>
-    </row>
-    <row r="32" ht="18" customHeight="1">
-      <c r="A32" s="40" t="inlineStr">
-        <is>
-          <t>GARITA</t>
-        </is>
-      </c>
-      <c r="B32" s="43" t="n"/>
-      <c r="C32" s="43" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D32" s="146" t="n"/>
-      <c r="E32" s="133" t="n"/>
-      <c r="F32" s="133" t="n"/>
-      <c r="G32" s="133" t="n"/>
-      <c r="H32" s="133" t="n"/>
-      <c r="I32" s="133" t="n"/>
-      <c r="J32" s="133" t="n"/>
-      <c r="K32" s="134" t="n"/>
-    </row>
-    <row r="33" ht="18" customHeight="1">
-      <c r="A33" s="40" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CONO DE TRANSITO </t>
-        </is>
-      </c>
-      <c r="B33" s="43" t="n"/>
-      <c r="C33" s="43" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D33" s="146" t="n"/>
-      <c r="E33" s="133" t="n"/>
-      <c r="F33" s="133" t="n"/>
-      <c r="G33" s="133" t="n"/>
-      <c r="H33" s="133" t="n"/>
-      <c r="I33" s="133" t="n"/>
-      <c r="J33" s="133" t="n"/>
-      <c r="K33" s="134" t="n"/>
-    </row>
-    <row r="34" ht="18" customHeight="1">
-      <c r="A34" s="40" t="inlineStr">
-        <is>
-          <t>CAJA FUERTE</t>
-        </is>
-      </c>
-      <c r="B34" s="43" t="n"/>
-      <c r="C34" s="43" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D34" s="146" t="n"/>
-      <c r="E34" s="133" t="n"/>
-      <c r="F34" s="133" t="n"/>
-      <c r="G34" s="133" t="n"/>
-      <c r="H34" s="133" t="n"/>
-      <c r="I34" s="133" t="n"/>
-      <c r="J34" s="133" t="n"/>
-      <c r="K34" s="134" t="n"/>
-    </row>
-    <row r="35" ht="18" customHeight="1">
-      <c r="A35" s="40" t="inlineStr">
-        <is>
-          <t>CAJA METALICA</t>
-        </is>
-      </c>
-      <c r="B35" s="43" t="n"/>
-      <c r="C35" s="43" t="n">
-        <v>1</v>
-      </c>
-      <c r="D35" s="146" t="n"/>
-      <c r="E35" s="133" t="n"/>
-      <c r="F35" s="133" t="n"/>
-      <c r="G35" s="133" t="n"/>
-      <c r="H35" s="133" t="n"/>
-      <c r="I35" s="133" t="n"/>
-      <c r="J35" s="133" t="n"/>
-      <c r="K35" s="134" t="n"/>
-    </row>
-    <row r="36" ht="18" customHeight="1">
-      <c r="A36" s="40" t="inlineStr">
-        <is>
-          <t>CANDADO</t>
-        </is>
-      </c>
-      <c r="B36" s="43" t="n"/>
-      <c r="C36" s="43" t="n">
-        <v>1</v>
-      </c>
-      <c r="D36" s="146" t="n"/>
-      <c r="E36" s="133" t="n"/>
-      <c r="F36" s="133" t="n"/>
-      <c r="G36" s="133" t="n"/>
-      <c r="H36" s="133" t="n"/>
-      <c r="I36" s="133" t="n"/>
-      <c r="J36" s="133" t="n"/>
-      <c r="K36" s="134" t="n"/>
-    </row>
-    <row r="37" ht="18" customHeight="1">
-      <c r="A37" s="40" t="inlineStr">
-        <is>
-          <t>CARP. PROCEDIMIENTOS</t>
-        </is>
-      </c>
-      <c r="B37" s="43" t="n"/>
-      <c r="C37" s="43" t="n"/>
-      <c r="D37" s="146" t="n"/>
-      <c r="E37" s="133" t="n"/>
-      <c r="F37" s="133" t="n"/>
-      <c r="G37" s="133" t="n"/>
-      <c r="H37" s="133" t="n"/>
-      <c r="I37" s="133" t="n"/>
-      <c r="J37" s="133" t="n"/>
-      <c r="K37" s="134" t="n"/>
-    </row>
-    <row r="38" ht="18" customHeight="1">
-      <c r="A38" s="40" t="inlineStr">
-        <is>
-          <t>TABLEROS</t>
-        </is>
-      </c>
-      <c r="B38" s="43" t="n"/>
-      <c r="C38" s="43" t="n"/>
-      <c r="D38" s="146" t="n"/>
-      <c r="E38" s="133" t="n"/>
-      <c r="F38" s="133" t="n"/>
-      <c r="G38" s="133" t="n"/>
-      <c r="H38" s="133" t="n"/>
-      <c r="I38" s="133" t="n"/>
-      <c r="J38" s="133" t="n"/>
-      <c r="K38" s="134" t="n"/>
-    </row>
-    <row r="39" ht="18" customHeight="1">
-      <c r="A39" s="40" t="inlineStr">
-        <is>
-          <t>REGULADOR DE VOLTAJE</t>
-        </is>
-      </c>
-      <c r="B39" s="43" t="n"/>
-      <c r="C39" s="43" t="n"/>
-      <c r="D39" s="146" t="n"/>
-      <c r="E39" s="133" t="n"/>
-      <c r="F39" s="133" t="n"/>
-      <c r="G39" s="133" t="n"/>
-      <c r="H39" s="133" t="n"/>
-      <c r="I39" s="133" t="n"/>
-      <c r="J39" s="133" t="n"/>
-      <c r="K39" s="134" t="n"/>
-    </row>
-    <row r="40" ht="18" customHeight="1">
-      <c r="A40" s="24" t="inlineStr">
-        <is>
-          <t>PORTA CARTUCHOS</t>
-        </is>
-      </c>
-      <c r="B40" s="44" t="n"/>
-      <c r="C40" s="43" t="n">
-        <v>1</v>
-      </c>
-      <c r="D40" s="146" t="n"/>
-      <c r="E40" s="133" t="n"/>
-      <c r="F40" s="133" t="n"/>
-      <c r="G40" s="133" t="n"/>
-      <c r="H40" s="133" t="n"/>
-      <c r="I40" s="133" t="n"/>
-      <c r="J40" s="133" t="n"/>
-      <c r="K40" s="134" t="n"/>
-    </row>
-    <row r="41" ht="18" customHeight="1">
-      <c r="A41" s="24" t="inlineStr">
-        <is>
-          <t>PORTA ESCOPETA</t>
-        </is>
-      </c>
-      <c r="B41" s="44" t="n"/>
-      <c r="C41" s="43" t="n">
-        <v>1</v>
-      </c>
-      <c r="D41" s="146" t="n"/>
-      <c r="E41" s="133" t="n"/>
-      <c r="F41" s="133" t="n"/>
-      <c r="G41" s="133" t="n"/>
-      <c r="H41" s="133" t="n"/>
-      <c r="I41" s="133" t="n"/>
-      <c r="J41" s="133" t="n"/>
-      <c r="K41" s="134" t="n"/>
-    </row>
-    <row r="42" ht="18" customHeight="1">
-      <c r="A42" s="24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">OTROS: </t>
-        </is>
-      </c>
-      <c r="B42" s="44" t="n"/>
-      <c r="C42" s="43" t="n"/>
-      <c r="D42" s="146" t="n"/>
-      <c r="E42" s="133" t="n"/>
-      <c r="F42" s="133" t="n"/>
-      <c r="G42" s="133" t="n"/>
-      <c r="H42" s="133" t="n"/>
-      <c r="I42" s="133" t="n"/>
-      <c r="J42" s="133" t="n"/>
-      <c r="K42" s="134" t="n"/>
-    </row>
-    <row r="43" ht="21.75" customHeight="1">
-      <c r="A43" s="90" t="inlineStr">
-        <is>
-          <t>RESPONSABLES</t>
-        </is>
-      </c>
-      <c r="B43" s="133" t="n"/>
-      <c r="C43" s="133" t="n"/>
-      <c r="D43" s="133" t="n"/>
-      <c r="E43" s="133" t="n"/>
-      <c r="F43" s="133" t="n"/>
-      <c r="G43" s="133" t="n"/>
-      <c r="H43" s="133" t="n"/>
-      <c r="I43" s="133" t="n"/>
-      <c r="J43" s="133" t="n"/>
-      <c r="K43" s="133" t="n"/>
-    </row>
-    <row r="44" ht="69" customHeight="1">
-      <c r="A44" s="93" t="inlineStr">
-        <is>
-          <t>Me comprometo a utilizar mi equipo de dotacion, unicamente para el ejercicio de mis funciones en horario y turno asignado por GEVISE Cía. Ltda.
-En el caso de daño, deterioro por negligencia probada o cambio de dotación sin justificacion, acepto a las acciones disciplinarias que la empresa decida y asumo la responsabilidad que mis actos conlleven hacia terceras personas.</t>
-        </is>
-      </c>
-      <c r="B44" s="133" t="n"/>
-      <c r="C44" s="133" t="n"/>
-      <c r="D44" s="133" t="n"/>
-      <c r="E44" s="133" t="n"/>
-      <c r="F44" s="133" t="n"/>
-      <c r="G44" s="133" t="n"/>
-      <c r="H44" s="133" t="n"/>
-      <c r="I44" s="133" t="n"/>
-      <c r="J44" s="133" t="n"/>
-      <c r="K44" s="134" t="n"/>
-    </row>
-    <row r="45" ht="28.5" customHeight="1">
-      <c r="A45" s="22" t="inlineStr">
-        <is>
-          <t>GUARDIA 1</t>
-        </is>
-      </c>
-      <c r="B45" s="147" t="inlineStr">
-        <is>
-          <t>Nombre:</t>
-        </is>
-      </c>
-      <c r="C45" s="133" t="n"/>
-      <c r="D45" s="134" t="n"/>
-      <c r="E45" s="25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Firma: </t>
-        </is>
-      </c>
-      <c r="F45" s="48" t="n"/>
-      <c r="G45" s="133" t="n"/>
-      <c r="H45" s="133" t="n"/>
-      <c r="I45" s="133" t="n"/>
-      <c r="J45" s="133" t="n"/>
-      <c r="K45" s="134" t="n"/>
-    </row>
-    <row r="46" ht="28.5" customHeight="1">
-      <c r="A46" s="22" t="inlineStr">
-        <is>
-          <t>GUARDIA 2</t>
-        </is>
-      </c>
-      <c r="B46" s="147" t="inlineStr">
-        <is>
-          <t>Nombre:</t>
-        </is>
-      </c>
-      <c r="C46" s="133" t="n"/>
-      <c r="D46" s="134" t="n"/>
-      <c r="E46" s="25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Firma: </t>
-        </is>
-      </c>
-      <c r="F46" s="48" t="n"/>
-      <c r="G46" s="133" t="n"/>
-      <c r="H46" s="133" t="n"/>
-      <c r="I46" s="133" t="n"/>
-      <c r="J46" s="133" t="n"/>
-      <c r="K46" s="134" t="n"/>
-    </row>
-    <row r="47" ht="28.5" customHeight="1">
-      <c r="A47" s="22" t="inlineStr">
-        <is>
-          <t>GUARDIA 3</t>
-        </is>
-      </c>
-      <c r="B47" s="147" t="inlineStr">
-        <is>
-          <t>Nombre:</t>
-        </is>
-      </c>
-      <c r="C47" s="133" t="n"/>
-      <c r="D47" s="134" t="n"/>
-      <c r="E47" s="25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Firma: </t>
-        </is>
-      </c>
-      <c r="F47" s="48" t="n"/>
-      <c r="G47" s="133" t="n"/>
-      <c r="H47" s="133" t="n"/>
-      <c r="I47" s="133" t="n"/>
-      <c r="J47" s="133" t="n"/>
-      <c r="K47" s="134" t="n"/>
-    </row>
-    <row r="48" ht="32.25" customHeight="1">
-      <c r="A48" s="83" t="inlineStr">
-        <is>
-          <t>NOMBRE:</t>
-        </is>
-      </c>
-      <c r="B48" s="133" t="n"/>
-      <c r="C48" s="133" t="n"/>
-      <c r="D48" s="133" t="n"/>
-      <c r="E48" s="134" t="n"/>
-      <c r="F48" s="84" t="inlineStr">
-        <is>
-          <t>FIRMA:</t>
-        </is>
-      </c>
-      <c r="G48" s="126" t="n"/>
-      <c r="H48" s="126" t="n"/>
-      <c r="I48" s="126" t="n"/>
-      <c r="J48" s="126" t="n"/>
-      <c r="K48" s="127" t="n"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="83" t="inlineStr">
-        <is>
-          <t>CARGO:</t>
-        </is>
-      </c>
-      <c r="B49" s="126" t="n"/>
-      <c r="C49" s="126" t="n"/>
-      <c r="D49" s="126" t="n"/>
-      <c r="E49" s="127" t="n"/>
-      <c r="F49" s="128" t="n"/>
-      <c r="K49" s="129" t="n"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="130" t="n"/>
-      <c r="B50" s="131" t="n"/>
-      <c r="C50" s="131" t="n"/>
-      <c r="D50" s="131" t="n"/>
-      <c r="E50" s="132" t="n"/>
-      <c r="F50" s="130" t="n"/>
-      <c r="G50" s="131" t="n"/>
-      <c r="H50" s="131" t="n"/>
-      <c r="I50" s="131" t="n"/>
-      <c r="J50" s="131" t="n"/>
-      <c r="K50" s="132" t="n"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="49" t="n"/>
-      <c r="D51" s="26" t="n"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="85" t="n"/>
-      <c r="D52" s="27" t="n"/>
-    </row>
-    <row r="56" ht="16.5" customHeight="1" thickBot="1">
-      <c r="C56" s="47" t="n"/>
-      <c r="D56" s="47" t="n"/>
-      <c r="E56" s="47" t="n"/>
-    </row>
-    <row r="57">
-      <c r="C57" s="80" t="inlineStr">
-        <is>
-          <t>FIRMA RESPONSABLE</t>
-        </is>
-      </c>
-      <c r="D57" s="148" t="n"/>
-      <c r="E57" s="148" t="n"/>
-    </row>
-  </sheetData>
-  <mergeCells count="60">
-    <mergeCell ref="D20:K20"/>
-    <mergeCell ref="D26:K26"/>
-    <mergeCell ref="A48:E48"/>
-    <mergeCell ref="F3:K3"/>
-    <mergeCell ref="J5:K5"/>
-    <mergeCell ref="D19:K19"/>
-    <mergeCell ref="D34:K34"/>
-    <mergeCell ref="A51:B51"/>
-    <mergeCell ref="F45:K45"/>
-    <mergeCell ref="D10:K10"/>
-    <mergeCell ref="D22:K22"/>
-    <mergeCell ref="F2:K2"/>
-    <mergeCell ref="D31:K31"/>
-    <mergeCell ref="D40:K40"/>
-    <mergeCell ref="D36:K36"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="F47:K47"/>
-    <mergeCell ref="D21:K21"/>
-    <mergeCell ref="F46:K46"/>
-    <mergeCell ref="D11:K11"/>
-    <mergeCell ref="F4:I4"/>
-    <mergeCell ref="D13:K13"/>
-    <mergeCell ref="D27:K27"/>
-    <mergeCell ref="D41:K41"/>
-    <mergeCell ref="D32:K32"/>
-    <mergeCell ref="D17:K17"/>
-    <mergeCell ref="J4:K4"/>
-    <mergeCell ref="C57:E57"/>
-    <mergeCell ref="B45:D45"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="D16:K16"/>
-    <mergeCell ref="D28:K28"/>
-    <mergeCell ref="A49:E50"/>
-    <mergeCell ref="F48:K50"/>
-    <mergeCell ref="D37:K37"/>
-    <mergeCell ref="F5:I5"/>
-    <mergeCell ref="B47:D47"/>
-    <mergeCell ref="D18:K18"/>
-    <mergeCell ref="D12:K12"/>
-    <mergeCell ref="B3:D3"/>
-    <mergeCell ref="A7:A9"/>
-    <mergeCell ref="A52:B52"/>
-    <mergeCell ref="D39:K39"/>
-    <mergeCell ref="D30:K30"/>
-    <mergeCell ref="D25:K25"/>
-    <mergeCell ref="D15:K15"/>
-    <mergeCell ref="D33:K33"/>
-    <mergeCell ref="F6:K6"/>
-    <mergeCell ref="B1:K1"/>
-    <mergeCell ref="D24:K24"/>
-    <mergeCell ref="D42:K42"/>
-    <mergeCell ref="A43:K43"/>
-    <mergeCell ref="D38:K38"/>
-    <mergeCell ref="B46:D46"/>
-    <mergeCell ref="D14:K14"/>
-    <mergeCell ref="D29:K29"/>
-    <mergeCell ref="D23:K23"/>
-    <mergeCell ref="A44:K44"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="D35:K35"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="56"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:L57"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15.75"/>
-  <cols>
-    <col width="34.28515625" customWidth="1" style="21" min="1" max="1"/>
-    <col width="14.5703125" customWidth="1" style="21" min="2" max="3"/>
-    <col width="17.7109375" customWidth="1" style="21" min="4" max="4"/>
-    <col width="23" customWidth="1" style="21" min="5" max="5"/>
-    <col width="8.7109375" customWidth="1" style="21" min="6" max="11"/>
-    <col width="11.42578125" customWidth="1" style="21" min="12" max="16384"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="60" customHeight="1">
-      <c r="A1" s="20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">LINTERNA </t>
-        </is>
-      </c>
-      <c r="B1" s="139" t="inlineStr">
-        <is>
-          <t>CONTROL DE INVENTARIOS
-Pag 1 de 1</t>
-        </is>
-      </c>
-      <c r="C1" s="133" t="n"/>
-      <c r="D1" s="133" t="n"/>
-      <c r="E1" s="133" t="n"/>
-      <c r="F1" s="133" t="n"/>
-      <c r="G1" s="133" t="n"/>
-      <c r="H1" s="133" t="n"/>
-      <c r="I1" s="133" t="n"/>
-      <c r="J1" s="133" t="n"/>
-      <c r="K1" s="134" t="n"/>
-      <c r="L1" s="42" t="n"/>
-    </row>
-    <row r="2" ht="20.25" customHeight="1">
-      <c r="A2" s="36" t="inlineStr">
-        <is>
-          <t>FECHA</t>
-        </is>
-      </c>
-      <c r="B2" s="140" t="n"/>
-      <c r="C2" s="133" t="n"/>
-      <c r="D2" s="134" t="n"/>
-      <c r="E2" s="36" t="inlineStr">
-        <is>
-          <t>SERVICIO</t>
-        </is>
-      </c>
-      <c r="F2" s="141" t="n"/>
-      <c r="G2" s="133" t="n"/>
-      <c r="H2" s="133" t="n"/>
-      <c r="I2" s="133" t="n"/>
-      <c r="J2" s="133" t="n"/>
-      <c r="K2" s="134" t="n"/>
-    </row>
-    <row r="3" ht="34.5" customHeight="1">
-      <c r="A3" s="37" t="inlineStr">
-        <is>
-          <t>CLIENTE</t>
-        </is>
-      </c>
-      <c r="B3" s="142" t="inlineStr"/>
-      <c r="C3" s="133" t="n"/>
-      <c r="D3" s="134" t="n"/>
-      <c r="E3" s="37" t="inlineStr">
-        <is>
-          <t>SIGLA</t>
-        </is>
-      </c>
-      <c r="F3" s="143" t="inlineStr">
-        <is>
-          <t>ORO 562</t>
-        </is>
-      </c>
-      <c r="G3" s="133" t="n"/>
-      <c r="H3" s="133" t="n"/>
-      <c r="I3" s="133" t="n"/>
-      <c r="J3" s="133" t="n"/>
-      <c r="K3" s="134" t="n"/>
-    </row>
-    <row r="4" ht="18" customHeight="1">
-      <c r="A4" s="144" t="inlineStr">
-        <is>
-          <t>ARMAMENTO</t>
-        </is>
-      </c>
-      <c r="B4" s="28" t="inlineStr">
-        <is>
-          <t>TIPO</t>
-        </is>
-      </c>
-      <c r="C4" s="31" t="inlineStr">
-        <is>
-          <t>CALIBRE</t>
-        </is>
-      </c>
-      <c r="D4" s="28" t="inlineStr">
-        <is>
-          <t>MARCA</t>
-        </is>
-      </c>
-      <c r="E4" s="61" t="inlineStr">
-        <is>
-          <t>SERIE</t>
-        </is>
-      </c>
-      <c r="F4" s="28" t="inlineStr">
-        <is>
-          <t>PERMISO</t>
-        </is>
-      </c>
-      <c r="G4" s="133" t="n"/>
-      <c r="H4" s="133" t="n"/>
-      <c r="I4" s="134" t="n"/>
-      <c r="J4" s="28" t="inlineStr">
-        <is>
-          <t>VIGENCIA</t>
-        </is>
-      </c>
-      <c r="K4" s="134" t="n"/>
-    </row>
-    <row r="5" ht="33.75" customHeight="1">
-      <c r="A5" s="132" t="n"/>
-      <c r="B5" s="33" t="n"/>
-      <c r="C5" s="33" t="n"/>
-      <c r="D5" s="33" t="n"/>
-      <c r="E5" s="33" t="inlineStr"/>
-      <c r="F5" s="33" t="n"/>
-      <c r="G5" s="133" t="n"/>
-      <c r="H5" s="133" t="n"/>
-      <c r="I5" s="134" t="n"/>
-      <c r="J5" s="145" t="n"/>
-      <c r="K5" s="134" t="n"/>
-    </row>
-    <row r="6" ht="24.75" customHeight="1">
-      <c r="A6" s="86" t="inlineStr">
-        <is>
-          <t>MUNICIONES</t>
-        </is>
-      </c>
-      <c r="B6" s="39" t="inlineStr">
-        <is>
-          <t>CANT</t>
-        </is>
-      </c>
-      <c r="C6" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" s="39" t="inlineStr">
-        <is>
-          <t>OBSERVACION</t>
-        </is>
-      </c>
-      <c r="E6" s="134" t="n"/>
-      <c r="F6" s="33" t="n"/>
-      <c r="G6" s="133" t="n"/>
-      <c r="H6" s="133" t="n"/>
-      <c r="I6" s="133" t="n"/>
-      <c r="J6" s="133" t="n"/>
-      <c r="K6" s="134" t="n"/>
-    </row>
-    <row r="7" ht="81" customHeight="1">
-      <c r="A7" s="144" t="inlineStr">
-        <is>
-          <t>COMUNICACIÓN</t>
-        </is>
-      </c>
-      <c r="B7" s="34" t="inlineStr">
-        <is>
-          <t>TIPO</t>
-        </is>
-      </c>
-      <c r="C7" s="34" t="inlineStr">
-        <is>
-          <t>MARCA</t>
-        </is>
-      </c>
-      <c r="D7" s="34" t="inlineStr">
-        <is>
-          <t>MODELO</t>
-        </is>
-      </c>
-      <c r="E7" s="34" t="inlineStr">
-        <is>
-          <t>SERIE</t>
-        </is>
-      </c>
-      <c r="F7" s="35" t="inlineStr">
-        <is>
-          <t>PERILLA</t>
-        </is>
-      </c>
-      <c r="G7" s="35" t="inlineStr">
-        <is>
-          <t>PTT</t>
-        </is>
-      </c>
-      <c r="H7" s="35" t="inlineStr">
-        <is>
-          <t>ANTENA</t>
-        </is>
-      </c>
-      <c r="I7" s="35" t="inlineStr">
-        <is>
-          <t>BATERIA</t>
-        </is>
-      </c>
-      <c r="J7" s="35" t="inlineStr">
-        <is>
-          <t>CARGADOR</t>
-        </is>
-      </c>
-      <c r="K7" s="35" t="inlineStr">
-        <is>
-          <t>BINCHA</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="22.5" customHeight="1">
-      <c r="A8" s="129" t="n"/>
-      <c r="B8" s="45" t="inlineStr">
-        <is>
-          <t>RADIO</t>
-        </is>
-      </c>
-      <c r="C8" s="46" t="inlineStr">
-        <is>
-          <t>MOTOROLA</t>
-        </is>
-      </c>
-      <c r="D8" s="45" t="inlineStr">
-        <is>
-          <t>DEP 450</t>
-        </is>
-      </c>
-      <c r="E8" s="45" t="inlineStr">
-        <is>
-          <t>752EYQA172</t>
-        </is>
-      </c>
-      <c r="F8" s="45" t="n"/>
-      <c r="G8" s="45" t="n"/>
-      <c r="H8" s="45" t="n"/>
-      <c r="I8" s="45" t="n"/>
-      <c r="J8" s="45" t="n"/>
-      <c r="K8" s="45" t="n"/>
-    </row>
-    <row r="9" ht="21" customHeight="1">
-      <c r="A9" s="132" t="n"/>
-      <c r="B9" s="45" t="n"/>
-      <c r="C9" s="46" t="n"/>
-      <c r="D9" s="45" t="n"/>
-      <c r="E9" s="45" t="n"/>
-      <c r="F9" s="45" t="n"/>
-      <c r="G9" s="45" t="n"/>
-      <c r="H9" s="45" t="n"/>
-      <c r="I9" s="45" t="n"/>
-      <c r="J9" s="45" t="n"/>
-      <c r="K9" s="45" t="n"/>
-    </row>
-    <row r="10" ht="65.25" customHeight="1">
-      <c r="A10" s="30" t="inlineStr">
-        <is>
-          <t>DOTACION</t>
-        </is>
-      </c>
-      <c r="B10" s="23" t="inlineStr">
-        <is>
-          <t>BUENO
-MALO
-REGULAR
-NO TIENE</t>
-        </is>
-      </c>
-      <c r="C10" s="29" t="inlineStr">
-        <is>
-          <t>CANT</t>
-        </is>
-      </c>
-      <c r="D10" s="30" t="inlineStr">
-        <is>
-          <t>OBSERVACION</t>
-        </is>
-      </c>
-      <c r="E10" s="133" t="n"/>
-      <c r="F10" s="133" t="n"/>
-      <c r="G10" s="133" t="n"/>
-      <c r="H10" s="133" t="n"/>
-      <c r="I10" s="133" t="n"/>
-      <c r="J10" s="133" t="n"/>
-      <c r="K10" s="134" t="n"/>
-    </row>
-    <row r="11" ht="18" customHeight="1">
-      <c r="A11" s="40" t="inlineStr">
-        <is>
-          <t>BITACORA</t>
-        </is>
-      </c>
-      <c r="B11" s="43" t="n"/>
-      <c r="C11" s="43" t="n"/>
-      <c r="D11" s="146" t="n"/>
-      <c r="E11" s="133" t="n"/>
-      <c r="F11" s="133" t="n"/>
-      <c r="G11" s="133" t="n"/>
-      <c r="H11" s="133" t="n"/>
-      <c r="I11" s="133" t="n"/>
-      <c r="J11" s="133" t="n"/>
-      <c r="K11" s="134" t="n"/>
-    </row>
-    <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="40" t="inlineStr">
-        <is>
-          <t xml:space="preserve">FORRO DE CHALECO </t>
-        </is>
-      </c>
-      <c r="B12" s="43" t="n"/>
-      <c r="C12" s="43" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C12" s="43" t="n">
+        <v>2</v>
       </c>
       <c r="D12" s="146" t="n"/>
       <c r="E12" s="133" t="n"/>
